--- a/simulations/correction_peat_market/sscons_ssinv_vf.xlsx
+++ b/simulations/correction_peat_market/sscons_ssinv_vf.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Users\hravoaha\Desktop\Thèse\Thèse 2023\Objectif 2\biowaste_optim\simulations\correction_peat_market\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A3F9D4B9-3453-44F2-9EFF-54E2EFDAE889}" xr6:coauthVersionLast="36" xr6:coauthVersionMax="36" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{1E25BED3-BEA3-4EE3-93CB-63A3D432D57E}" xr6:coauthVersionLast="36" xr6:coauthVersionMax="36" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="0" windowWidth="19200" windowHeight="8150" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView minimized="1" xWindow="0" yWindow="0" windowWidth="19200" windowHeight="8150" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="results" sheetId="1" r:id="rId1"/>
@@ -20,7 +20,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="56" uniqueCount="46">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="56" uniqueCount="47">
   <si>
     <t>HC</t>
   </si>
@@ -158,6 +158,9 @@
   </si>
   <si>
     <t>AD-biomet-dig</t>
+  </si>
+  <si>
+    <t>minCC</t>
   </si>
 </sst>
 </file>
@@ -248,6 +251,15 @@
     <xf numFmtId="2" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
     <xf numFmtId="11" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="3" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyBorder="1" applyAlignment="1">
@@ -255,15 +267,6 @@
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="3" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="3" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -363,7 +366,7 @@
               <c:strCache>
                 <c:ptCount val="7"/>
                 <c:pt idx="0">
-                  <c:v>minCO2</c:v>
+                  <c:v>minCC</c:v>
                 </c:pt>
                 <c:pt idx="1">
                   <c:v>minEQ</c:v>
@@ -452,7 +455,7 @@
               <c:strCache>
                 <c:ptCount val="7"/>
                 <c:pt idx="0">
-                  <c:v>minCO2</c:v>
+                  <c:v>minCC</c:v>
                 </c:pt>
                 <c:pt idx="1">
                   <c:v>minEQ</c:v>
@@ -541,7 +544,7 @@
               <c:strCache>
                 <c:ptCount val="7"/>
                 <c:pt idx="0">
-                  <c:v>minCO2</c:v>
+                  <c:v>minCC</c:v>
                 </c:pt>
                 <c:pt idx="1">
                   <c:v>minEQ</c:v>
@@ -630,7 +633,7 @@
               <c:strCache>
                 <c:ptCount val="7"/>
                 <c:pt idx="0">
-                  <c:v>minCO2</c:v>
+                  <c:v>minCC</c:v>
                 </c:pt>
                 <c:pt idx="1">
                   <c:v>minEQ</c:v>
@@ -1773,47 +1776,47 @@
   <sheetData>
     <row r="1" spans="1:40" x14ac:dyDescent="0.35">
       <c r="A1" s="2"/>
-      <c r="B1" s="5"/>
-      <c r="C1" s="6"/>
-      <c r="D1" s="5" t="s">
+      <c r="B1" s="8"/>
+      <c r="C1" s="9"/>
+      <c r="D1" s="8" t="s">
         <v>0</v>
       </c>
-      <c r="E1" s="7"/>
-      <c r="F1" s="7"/>
-      <c r="G1" s="7"/>
-      <c r="H1" s="7"/>
-      <c r="I1" s="7"/>
-      <c r="J1" s="7"/>
-      <c r="K1" s="7"/>
-      <c r="L1" s="7"/>
-      <c r="M1" s="7"/>
-      <c r="N1" s="7"/>
-      <c r="O1" s="7"/>
-      <c r="P1" s="7"/>
-      <c r="Q1" s="7"/>
-      <c r="R1" s="7"/>
-      <c r="S1" s="7"/>
-      <c r="T1" s="7"/>
-      <c r="U1" s="7"/>
-      <c r="V1" s="7"/>
-      <c r="W1" s="7"/>
-      <c r="X1" s="7"/>
-      <c r="Y1" s="6"/>
-      <c r="Z1" s="5" t="s">
+      <c r="E1" s="10"/>
+      <c r="F1" s="10"/>
+      <c r="G1" s="10"/>
+      <c r="H1" s="10"/>
+      <c r="I1" s="10"/>
+      <c r="J1" s="10"/>
+      <c r="K1" s="10"/>
+      <c r="L1" s="10"/>
+      <c r="M1" s="10"/>
+      <c r="N1" s="10"/>
+      <c r="O1" s="10"/>
+      <c r="P1" s="10"/>
+      <c r="Q1" s="10"/>
+      <c r="R1" s="10"/>
+      <c r="S1" s="10"/>
+      <c r="T1" s="10"/>
+      <c r="U1" s="10"/>
+      <c r="V1" s="10"/>
+      <c r="W1" s="10"/>
+      <c r="X1" s="10"/>
+      <c r="Y1" s="9"/>
+      <c r="Z1" s="8" t="s">
         <v>1</v>
       </c>
-      <c r="AA1" s="6"/>
+      <c r="AA1" s="9"/>
       <c r="AB1" s="2" t="s">
         <v>2</v>
       </c>
-      <c r="AC1" s="8" t="s">
+      <c r="AC1" s="5" t="s">
         <v>3</v>
       </c>
-      <c r="AD1" s="9"/>
-      <c r="AE1" s="9"/>
-      <c r="AF1" s="9"/>
-      <c r="AG1" s="9"/>
-      <c r="AH1" s="10"/>
+      <c r="AD1" s="6"/>
+      <c r="AE1" s="6"/>
+      <c r="AF1" s="6"/>
+      <c r="AG1" s="6"/>
+      <c r="AH1" s="7"/>
     </row>
     <row r="2" spans="1:40" x14ac:dyDescent="0.35">
       <c r="A2" s="2"/>
@@ -2030,7 +2033,7 @@
         <v>0.83131192868738812</v>
       </c>
       <c r="AJ3" t="s">
-        <v>37</v>
+        <v>46</v>
       </c>
       <c r="AK3">
         <f>SUM(D3:Y3)</f>
